--- a/data/b2_indio/B2 Índio 09-2026.xlsx
+++ b/data/b2_indio/B2 Índio 09-2026.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MOVIMENTO DIÁRIO'!$A$1:$H$109</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'COMPRAS'!$A$1:$G$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'COMPRAS'!$A$1:$G$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DESPESAS'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3737,7 +3737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4139,60 +4139,87 @@
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gasolina Comum</t>
+          <t>Etanol</t>
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>5.7589</v>
+        <v>3.9693</v>
       </c>
       <c r="E15" s="17" t="n">
-        <v>143973.57</v>
+        <v>59539.89</v>
       </c>
       <c r="F15" t="n">
-        <v>244328</v>
+        <v>244259</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Distribuidora Alfa</t>
+          <t>Distribuidora Paraná</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>5.7589</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>143973.57</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>244328</v>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>Distribuidora Alfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n">
         <v>46291</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Gasolina Aditivada</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C17" s="13" t="n">
         <v>5000</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D17" s="14" t="n">
         <v>5.9016</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>29507.86</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F17" t="n">
         <v>244365</v>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Distribuidora Paraná</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G16"/>
+  <autoFilter ref="A1:G17"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list">
       <formula1>"Gasolina Comum,Gasolina Aditivada,Etanol,Diesel S10"</formula1>

--- a/data/b2_indio/B2 Índio 09-2026.xlsx
+++ b/data/b2_indio/B2 Índio 09-2026.xlsx
@@ -13,9 +13,9 @@
     <sheet name="DESPESAS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MOVIMENTO DIÁRIO'!$A$1:$H$109</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'COMPRAS'!$A$1:$G$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DESPESAS'!$A$1:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MOVIMENTO DIÁRIO'!$A$1:$H$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'COMPRAS'!$A$1:$G$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DESPESAS'!$A$1:$D$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -641,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3720,8 +3720,344 @@
         <v>6.583</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="7" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="n">
+        <v>28102</v>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="9" t="n">
+        <v>3648</v>
+      </c>
+      <c r="F110" s="9" t="n">
+        <v>24451</v>
+      </c>
+      <c r="G110" s="10" t="n">
+        <v>5.764</v>
+      </c>
+      <c r="H110" s="11" t="n">
+        <v>6.384</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C111" s="13" t="n">
+        <v>9504</v>
+      </c>
+      <c r="D111" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="13" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F111" s="13" t="n">
+        <v>8453</v>
+      </c>
+      <c r="G111" s="14" t="n">
+        <v>5.9068</v>
+      </c>
+      <c r="H111" s="15" t="n">
+        <v>6.779</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="n">
+        <v>14775</v>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="9" t="n">
+        <v>1667</v>
+      </c>
+      <c r="F112" s="9" t="n">
+        <v>13108</v>
+      </c>
+      <c r="G112" s="10" t="n">
+        <v>3.9696</v>
+      </c>
+      <c r="H112" s="11" t="n">
+        <v>4.583</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Diesel S10</t>
+        </is>
+      </c>
+      <c r="C113" s="13" t="n">
+        <v>27877</v>
+      </c>
+      <c r="D113" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="13" t="n">
+        <v>2086</v>
+      </c>
+      <c r="F113" s="13" t="n">
+        <v>25792</v>
+      </c>
+      <c r="G113" s="14" t="n">
+        <v>5.9971</v>
+      </c>
+      <c r="H113" s="15" t="n">
+        <v>6.584</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="n">
+        <v>24451</v>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="9" t="n">
+        <v>3575</v>
+      </c>
+      <c r="F114" s="9" t="n">
+        <v>20868</v>
+      </c>
+      <c r="G114" s="10" t="n">
+        <v>5.764</v>
+      </c>
+      <c r="H114" s="11" t="n">
+        <v>6.38</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C115" s="13" t="n">
+        <v>8453</v>
+      </c>
+      <c r="D115" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="13" t="n">
+        <v>1017</v>
+      </c>
+      <c r="F115" s="13" t="n">
+        <v>7434</v>
+      </c>
+      <c r="G115" s="14" t="n">
+        <v>5.9068</v>
+      </c>
+      <c r="H115" s="15" t="n">
+        <v>6.786</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="n">
+        <v>13108</v>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="9" t="n">
+        <v>1822</v>
+      </c>
+      <c r="F116" s="9" t="n">
+        <v>11286</v>
+      </c>
+      <c r="G116" s="10" t="n">
+        <v>3.9696</v>
+      </c>
+      <c r="H116" s="11" t="n">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Diesel S10</t>
+        </is>
+      </c>
+      <c r="C117" s="13" t="n">
+        <v>25792</v>
+      </c>
+      <c r="D117" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="13" t="n">
+        <v>2293</v>
+      </c>
+      <c r="F117" s="13" t="n">
+        <v>23500</v>
+      </c>
+      <c r="G117" s="14" t="n">
+        <v>5.9971</v>
+      </c>
+      <c r="H117" s="15" t="n">
+        <v>6.586</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="n">
+        <v>20868</v>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="9" t="n">
+        <v>3299</v>
+      </c>
+      <c r="F118" s="9" t="n">
+        <v>17565</v>
+      </c>
+      <c r="G118" s="10" t="n">
+        <v>5.764</v>
+      </c>
+      <c r="H118" s="11" t="n">
+        <v>6.385</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C119" s="13" t="n">
+        <v>7434</v>
+      </c>
+      <c r="D119" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="13" t="n">
+        <v>856</v>
+      </c>
+      <c r="F119" s="13" t="n">
+        <v>6578</v>
+      </c>
+      <c r="G119" s="14" t="n">
+        <v>5.9068</v>
+      </c>
+      <c r="H119" s="15" t="n">
+        <v>6.782</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="n">
+        <v>11286</v>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E120" s="9" t="n">
+        <v>1571</v>
+      </c>
+      <c r="F120" s="9" t="n">
+        <v>24714</v>
+      </c>
+      <c r="G120" s="10" t="n">
+        <v>3.9953</v>
+      </c>
+      <c r="H120" s="11" t="n">
+        <v>4.588</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="12" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Diesel S10</t>
+        </is>
+      </c>
+      <c r="C121" s="13" t="n">
+        <v>23500</v>
+      </c>
+      <c r="D121" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="13" t="n">
+        <v>2016</v>
+      </c>
+      <c r="F121" s="13" t="n">
+        <v>21484</v>
+      </c>
+      <c r="G121" s="14" t="n">
+        <v>5.9971</v>
+      </c>
+      <c r="H121" s="15" t="n">
+        <v>6.584</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H109"/>
+  <autoFilter ref="A1:H121"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list">
       <formula1>"Gasolina Comum,Gasolina Aditivada,Etanol,Diesel S10"</formula1>
@@ -3737,7 +4073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4218,8 +4554,35 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>4.0147</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>60220.41</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>244395</v>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>Distribuidora Sul</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G18"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list">
       <formula1>"Gasolina Comum,Gasolina Aditivada,Etanol,Diesel S10"</formula1>
@@ -4235,7 +4598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4281,7 +4644,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>51774.13</v>
+        <v>51142.27</v>
       </c>
     </row>
     <row r="3">
@@ -4290,178 +4653,178 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Limpeza da caixa separadora</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>2691.19</v>
+        <v>2851.97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>2574.07</v>
+        <v>1332.18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uniformes e EPI</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>977.15</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3900</v>
+        <v>2195.71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>2097.72</v>
+        <v>2819.74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>3184.7</v>
+        <v>9808.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>2652.02</v>
+        <v>1482.54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>9636.969999999999</v>
+        <v>1514.03</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46280</v>
+        <v>46285</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1321.38</v>
+        <v>18510.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Manutenção preventiva das bombas</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>1410.48</v>
+        <v>4049.82</v>
       </c>
     </row>
     <row r="13">
@@ -4470,39 +4833,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>18315.02</v>
+        <v>2666.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>2740</v>
+        <v>2612.44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46291</v>
+        <v>46287</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -4511,11 +4874,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Seguro do posto</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>832.9</v>
+        <v>814.2</v>
       </c>
     </row>
     <row r="16">
@@ -4533,11 +4896,29 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>2584.29</v>
+        <v>2448.15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Taxas de cartão</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Taxas das maquininhas (semana)</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>1133.28</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D16"/>
+  <autoFilter ref="A1:D17"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list">
       <formula1>"Folha de pagamento,Aluguel,Energia elétrica,Água e esgoto,Taxas de cartão,Manutenção,Fretes,Sistemas e contabilidade,Marketing,Outras despesas"</formula1>
